--- a/src/filesExcel/Pattern.xlsx
+++ b/src/filesExcel/Pattern.xlsx
@@ -7,7 +7,7 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12643"/>
   </bookViews>
   <sheets>
-    <sheet name="Лист1" sheetId="1" r:id="rId1"/>
+    <sheet name="Квалификация" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>

--- a/src/filesExcel/Pattern.xlsx
+++ b/src/filesExcel/Pattern.xlsx
@@ -2,12 +2,76 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+  <workbookPr filterPrivacy="1" codeName="ЭтаКнига" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12643"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12643" tabRatio="940" firstSheet="11" activeTab="11"/>
   </bookViews>
   <sheets>
     <sheet name="Квалификация" sheetId="1" r:id="rId1"/>
+    <sheet name="1,8финала 3Д_БЛ_Муж" sheetId="2" r:id="rId2"/>
+    <sheet name="1,8финала 3Д_БЛ_Жен" sheetId="3" r:id="rId3"/>
+    <sheet name="1,8финала 3Д_КЛ_Муж" sheetId="4" r:id="rId4"/>
+    <sheet name="1,8финала 3Д_КЛ_Жен" sheetId="5" r:id="rId5"/>
+    <sheet name="1,8финала 3Д-Long_Муж" sheetId="6" r:id="rId6"/>
+    <sheet name="1,8финала 3Д-Long_Жен" sheetId="7" r:id="rId7"/>
+    <sheet name="1,8финала 3Д-Составной_Муж" sheetId="8" r:id="rId8"/>
+    <sheet name="1,8финала 3Д-Составной_Жен" sheetId="9" r:id="rId9"/>
+    <sheet name="1,8финала 3Д-Sporting_Муж" sheetId="10" r:id="rId10"/>
+    <sheet name="1,8финала 3Д-Sporting_Жен" sheetId="11" r:id="rId11"/>
+    <sheet name="1,8финала 3Д-исторический_Муж" sheetId="44" r:id="rId12"/>
+    <sheet name="1,8финала 3Д-исторический_Жен" sheetId="45" r:id="rId13"/>
+    <sheet name="1,8финала 3Д-олимпик_Муж" sheetId="46" r:id="rId14"/>
+    <sheet name="1,8финала 3Д-олимпик_Жен" sheetId="47" r:id="rId15"/>
+    <sheet name="1,8финала 3Д-арбалет_Муж" sheetId="48" r:id="rId16"/>
+    <sheet name="1,8финала 3Д-арбалет_Жен" sheetId="49" r:id="rId17"/>
+    <sheet name="1,4финала 3Д_БЛ_Муж" sheetId="12" r:id="rId18"/>
+    <sheet name="1,4финала 3Д_БЛ_Жен" sheetId="13" r:id="rId19"/>
+    <sheet name="1,4финала 3Д_КЛ_Муж" sheetId="14" r:id="rId20"/>
+    <sheet name="1,4финала 3Д_КЛ_Жен" sheetId="15" r:id="rId21"/>
+    <sheet name="1,4финала 3Д-Long_Муж" sheetId="16" r:id="rId22"/>
+    <sheet name="1,4финала 3Д-Long_Жен" sheetId="18" r:id="rId23"/>
+    <sheet name="1,4финала 3Д-Составной_Муж" sheetId="19" r:id="rId24"/>
+    <sheet name="1,4финала 3Д-Составной_Жен" sheetId="20" r:id="rId25"/>
+    <sheet name="1,4финала 3Д-Sporting_Муж" sheetId="21" r:id="rId26"/>
+    <sheet name="1,4финала 3Д-Sporting_Жен" sheetId="22" r:id="rId27"/>
+    <sheet name="1,4финала 3Д-исторический_Муж" sheetId="50" r:id="rId28"/>
+    <sheet name="1,4финала 3Д-исторический_Жен" sheetId="51" r:id="rId29"/>
+    <sheet name="1,4финала 3Д-олимпик_Муж" sheetId="52" r:id="rId30"/>
+    <sheet name="1,4финала 3Д-олимпик_Жен" sheetId="53" r:id="rId31"/>
+    <sheet name="1,4финала 3Д-арбалет_Муж" sheetId="54" r:id="rId32"/>
+    <sheet name="1,4финала 3Д-арбалет_Жен" sheetId="55" r:id="rId33"/>
+    <sheet name="1,2финала 3Д_БЛ_Муж" sheetId="24" r:id="rId34"/>
+    <sheet name="1,2финала 3Д_БЛ_Жен" sheetId="25" r:id="rId35"/>
+    <sheet name="1,2финала 3Д_КЛ_Муж" sheetId="26" r:id="rId36"/>
+    <sheet name="1,2финала 3Д_КЛ_Жен" sheetId="27" r:id="rId37"/>
+    <sheet name="1,2финала 3Д-Long_Муж" sheetId="28" r:id="rId38"/>
+    <sheet name="1,2финала 3Д-Long_Жен" sheetId="29" r:id="rId39"/>
+    <sheet name="1,2финала 3Д-Составной_Муж" sheetId="30" r:id="rId40"/>
+    <sheet name="1,2финала 3Д-Составной_Жен" sheetId="31" r:id="rId41"/>
+    <sheet name="1,2финала 3Д-Sporting_Муж" sheetId="32" r:id="rId42"/>
+    <sheet name="1,2финала 3Д-Sporting_Жен" sheetId="33" r:id="rId43"/>
+    <sheet name="1,2финала 3Д-Исторический_Муж" sheetId="56" r:id="rId44"/>
+    <sheet name="1,2финала 3Д-Исторический_Жен" sheetId="57" r:id="rId45"/>
+    <sheet name="1,2финала 3Д-Олимпик_Муж" sheetId="58" r:id="rId46"/>
+    <sheet name="1,2финала 3Д-Олимпик_Жен" sheetId="59" r:id="rId47"/>
+    <sheet name="1,2финала 3Д-Арбалет_Муж" sheetId="60" r:id="rId48"/>
+    <sheet name="1,2финала 3Д-Арбалет_Жен" sheetId="61" r:id="rId49"/>
+    <sheet name="Финал 3Д_БЛ_Муж" sheetId="34" r:id="rId50"/>
+    <sheet name="Финал 3Д_БЛ_Жен" sheetId="35" r:id="rId51"/>
+    <sheet name="Финал 3Д_КЛ_Муж" sheetId="36" r:id="rId52"/>
+    <sheet name="Финал 3Д_КЛ_Жен" sheetId="37" r:id="rId53"/>
+    <sheet name="Финал 3Д-Long_Муж" sheetId="38" r:id="rId54"/>
+    <sheet name="Финал 3Д-Long_Жен" sheetId="39" r:id="rId55"/>
+    <sheet name="Финал 3Д-Составной_Муж" sheetId="40" r:id="rId56"/>
+    <sheet name="Финал 3Д-Составной_Жен" sheetId="41" r:id="rId57"/>
+    <sheet name="Финал 3Д-Sporting_Муж" sheetId="42" r:id="rId58"/>
+    <sheet name="Финал 3Д-Sporting_Жен" sheetId="43" r:id="rId59"/>
+    <sheet name="Финал 3Д-Исторический_Муж" sheetId="62" r:id="rId60"/>
+    <sheet name="Финал 3Д-Исторический_Жен" sheetId="63" r:id="rId61"/>
+    <sheet name="Финала 3Д-Олимпик_Муж" sheetId="64" r:id="rId62"/>
+    <sheet name="Финала 3Д-Олимпик_Жен" sheetId="65" r:id="rId63"/>
+    <sheet name="Финала 3Д-Арбалет_Муж" sheetId="66" r:id="rId64"/>
+    <sheet name="Финала 3Д-Арбалет_Жен" sheetId="67" r:id="rId65"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -19,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="18">
   <si>
     <t>Кол-во участников:</t>
   </si>
@@ -59,6 +123,21 @@
   <si>
     <t>Класс лука</t>
   </si>
+  <si>
+    <t>Квал</t>
+  </si>
+  <si>
+    <t>Итог 1/8</t>
+  </si>
+  <si>
+    <t>Итог 1/4</t>
+  </si>
+  <si>
+    <t>Итог 1/2</t>
+  </si>
+  <si>
+    <t>Финал</t>
+  </si>
 </sst>
 </file>
 
@@ -88,7 +167,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -111,11 +190,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -126,6 +231,24 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -408,6 +531,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист1"/>
   <dimension ref="A1:M4"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -424,18 +548,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="5"/>
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9"/>
       <c r="C1" s="4"/>
       <c r="D1" s="3"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A2" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="5"/>
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9"/>
       <c r="C2" s="4"/>
       <c r="D2" s="3"/>
     </row>
@@ -487,4 +611,4508 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист10"/>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист11"/>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист12"/>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист13"/>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист2"/>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист14"/>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист15"/>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист16"/>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист17"/>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист18"/>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист19"/>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист20"/>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист21"/>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист3"/>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист22"/>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист23"/>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист24"/>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист25"/>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист26"/>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист27"/>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист4"/>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист28"/>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист29"/>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист30"/>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист31"/>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист5"/>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист32"/>
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="10" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист33"/>
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="10" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист34"/>
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="10" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист35"/>
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="10" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист36"/>
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="10" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист37"/>
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="10" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист38"/>
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="10" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист39"/>
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="10" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист40"/>
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="10" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист41"/>
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="10" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист6"/>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="10" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A1" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A2" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="11"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="10" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A1" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A2" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="11"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="10" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A1" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A2" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="11"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="10" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A1" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A2" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="11"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="10" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A1" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A2" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="11"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="10" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A1" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A2" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="11"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист7"/>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист8"/>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист9"/>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.69140625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.921875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.3046875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.3046875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="18.3046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="3"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>